--- a/data/trans_dic/IP17-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,99; 48,88</t>
+          <t>33,47; 48,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,36; 47,62</t>
+          <t>34,16; 48,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,38; 40,42</t>
+          <t>26,7; 40,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,75; 38,03</t>
+          <t>20,44; 37,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,57; 40,28</t>
+          <t>26,77; 40,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,16; 46,62</t>
+          <t>33,22; 46,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,31; 42,03</t>
+          <t>28,19; 42,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,06; 39,1</t>
+          <t>22,11; 39,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,61; 42,21</t>
+          <t>31,59; 41,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,9; 44,72</t>
+          <t>35,83; 45,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,7; 38,68</t>
+          <t>29,39; 39,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,83; 35,16</t>
+          <t>23,73; 36,26</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 24,3</t>
+          <t>15,65; 23,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,72; 28,36</t>
+          <t>19,0; 28,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 25,22</t>
+          <t>16,38; 25,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,87; 22,98</t>
+          <t>13,47; 23,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,07; 28,51</t>
+          <t>19,93; 28,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,0; 30,27</t>
+          <t>20,48; 29,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,33; 23,27</t>
+          <t>15,14; 23,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,28; 23,68</t>
+          <t>13,96; 24,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,96; 25,06</t>
+          <t>19,26; 25,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,13; 27,72</t>
+          <t>21,45; 27,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 22,7</t>
+          <t>17,04; 22,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,21; 21,52</t>
+          <t>14,81; 21,87</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 20,88</t>
+          <t>10,88; 21,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,8; 22,59</t>
+          <t>12,98; 22,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 22,82</t>
+          <t>12,95; 22,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,14; 24,83</t>
+          <t>13,18; 24,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,06; 25,35</t>
+          <t>14,53; 25,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 17,21</t>
+          <t>8,66; 17,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,59; 24,42</t>
+          <t>14,52; 23,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,76; 22,32</t>
+          <t>12,92; 22,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,11; 21,34</t>
+          <t>14,01; 21,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 18,27</t>
+          <t>11,98; 18,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,99; 21,49</t>
+          <t>15,31; 22,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,11; 21,67</t>
+          <t>14,38; 22,14</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 14,76</t>
+          <t>7,13; 14,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 16,96</t>
+          <t>8,36; 16,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 12,42</t>
+          <t>5,96; 12,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,44; 20,75</t>
+          <t>12,39; 20,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 18,52</t>
+          <t>10,22; 18,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 15,26</t>
+          <t>7,28; 15,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,24; 18,28</t>
+          <t>10,31; 18,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 16,17</t>
+          <t>10,68; 16,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,53; 16,59</t>
+          <t>10,51; 16,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 15,21</t>
+          <t>9,32; 15,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 14,12</t>
+          <t>9,43; 14,5</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,11</t>
+          <t>17,17; 21,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,42</t>
+          <t>20,5; 25,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 22,98</t>
+          <t>18,26; 23,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,55; 17,93</t>
+          <t>12,61; 18,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,96; 24,96</t>
+          <t>19,83; 24,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,18; 25,27</t>
+          <t>20,22; 25,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 22,11</t>
+          <t>17,47; 22,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,09; 19,64</t>
+          <t>14,87; 19,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 22,84</t>
+          <t>19,32; 22,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 24,67</t>
+          <t>21,02; 24,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,44; 21,8</t>
+          <t>18,33; 21,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 18,06</t>
+          <t>14,46; 18,2</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>43745</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60262</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44437</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16295</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40141</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58112</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42687</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>18447</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>83886</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>118374</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>87124</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>34742</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>35538; 51531</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50127; 70540</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35158; 52767</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11757; 21637</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>32497; 49274</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>48492; 67836</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>34820; 52027</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>13582; 24266</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>71893; 95020</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>104898; 132791</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>75001; 99541</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>28227; 43138</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>49802</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54949</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43195</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28198</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>61062</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67207</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48947</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>33728</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>110864</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>122156</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>92142</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>61925</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>39637; 60085</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44738; 66966</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>34474; 52670</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>21453; 37692</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>50584; 72754</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>54963; 78516</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>38970; 59833</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>25476; 44096</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>97628; 127921</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>108045; 140057</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>79747; 106725</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>50628; 74758</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>19738</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26967</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32733</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31296</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27442</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19852</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35739</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>36871</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>47181</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46819</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>68473</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>68167</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13877; 27030</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20296; 35906</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>24385; 42140</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22811; 43009</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>20566; 36641</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13673; 28225</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>27089; 44462</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>27464; 48259</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>37700; 58453</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>37659; 59584</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>57386; 82719</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>55444; 85362</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>20302</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20967</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23521</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>24526</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33191</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25410</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18746</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>42546</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>53494</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>46377</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>42266</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>67071</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13847; 27781</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14330; 28289</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17242; 31949</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16416; 34354</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>25527; 42554</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>18285; 33779</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>12621; 27089</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31487; 56161</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>42752; 64221</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>36823; 57464</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>32249; 53062</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>54767; 84217</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>133587</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>163145</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143886</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>100314</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>131592</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>295424</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>333726</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>290005</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>231906</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>116961; 149439</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145520; 180809</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>128350; 163278</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>83926; 120598</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>143277; 179505</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>151924; 189534</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>129406; 164987</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>113277; 149728</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>271234; 317509</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>307151; 360128</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>264740; 313988</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>206386; 259768</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP17-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,47; 48,54</t>
+          <t>33,12; 48,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,16; 48,06</t>
+          <t>35,19; 47,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 40,08</t>
+          <t>27,53; 40,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,44; 37,62</t>
+          <t>20,1; 37,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,77; 40,6</t>
+          <t>26,83; 39,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,22; 46,47</t>
+          <t>33,54; 46,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,19; 42,12</t>
+          <t>27,86; 41,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,11; 39,49</t>
+          <t>21,98; 40,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,59; 41,76</t>
+          <t>31,91; 41,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,83; 45,36</t>
+          <t>35,95; 45,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,39; 39,01</t>
+          <t>29,38; 38,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,73; 36,26</t>
+          <t>23,83; 35,51</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,65; 23,73</t>
+          <t>15,58; 23,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,0; 28,44</t>
+          <t>18,77; 27,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,38; 25,02</t>
+          <t>16,11; 24,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 23,66</t>
+          <t>13,17; 23,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,93; 28,67</t>
+          <t>19,86; 28,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,48; 29,26</t>
+          <t>21,11; 29,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 23,24</t>
+          <t>15,2; 23,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 24,15</t>
+          <t>14,11; 23,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,26; 25,23</t>
+          <t>18,94; 24,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,45; 27,8</t>
+          <t>20,94; 27,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,04; 22,8</t>
+          <t>17,02; 22,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 21,87</t>
+          <t>15,06; 21,91</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,88; 21,19</t>
+          <t>11,32; 21,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 22,96</t>
+          <t>12,97; 22,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,95; 22,38</t>
+          <t>13,45; 22,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 24,85</t>
+          <t>13,36; 24,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 25,89</t>
+          <t>14,71; 24,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,87</t>
+          <t>8,83; 17,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,52; 23,84</t>
+          <t>14,3; 23,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,92; 22,71</t>
+          <t>12,89; 22,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,01; 21,72</t>
+          <t>13,85; 21,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,98; 18,96</t>
+          <t>11,54; 18,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,31; 22,07</t>
+          <t>15,13; 21,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 22,14</t>
+          <t>14,3; 21,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 14,31</t>
+          <t>6,89; 14,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 16,51</t>
+          <t>8,34; 16,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 18,51</t>
+          <t>9,84; 18,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,47</t>
+          <t>5,74; 12,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 20,65</t>
+          <t>11,98; 20,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,22; 18,88</t>
+          <t>10,65; 18,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,63</t>
+          <t>7,32; 15,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,31; 18,38</t>
+          <t>10,59; 18,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 16,05</t>
+          <t>10,89; 16,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 16,4</t>
+          <t>10,59; 16,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 15,34</t>
+          <t>9,6; 15,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 14,5</t>
+          <t>9,15; 14,18</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 21,94</t>
+          <t>17,17; 22,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,5; 25,47</t>
+          <t>20,46; 25,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,22</t>
+          <t>18,16; 23,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 18,13</t>
+          <t>12,34; 17,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,83; 24,84</t>
+          <t>19,86; 24,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,22; 25,23</t>
+          <t>20,17; 25,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 22,27</t>
+          <t>17,53; 22,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,65</t>
+          <t>14,87; 19,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,32; 22,62</t>
+          <t>19,4; 22,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,02; 24,65</t>
+          <t>21,06; 24,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 21,75</t>
+          <t>18,47; 21,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 18,2</t>
+          <t>14,56; 18,08</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35538; 51531</t>
+          <t>35161; 51043</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50127; 70540</t>
+          <t>51639; 70321</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35158; 52767</t>
+          <t>36239; 53012</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11757; 21637</t>
+          <t>11560; 21816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32497; 49274</t>
+          <t>32564; 48263</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48492; 67836</t>
+          <t>48963; 68100</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34820; 52027</t>
+          <t>34414; 51118</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13582; 24266</t>
+          <t>13504; 24626</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71893; 95020</t>
+          <t>72605; 94637</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>104898; 132791</t>
+          <t>105250; 133365</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75001; 99541</t>
+          <t>74966; 98816</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28227; 43138</t>
+          <t>28347; 42241</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39637; 60085</t>
+          <t>39441; 60535</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44738; 66966</t>
+          <t>44211; 65674</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34474; 52670</t>
+          <t>33909; 51467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21453; 37692</t>
+          <t>20977; 37554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50584; 72754</t>
+          <t>50392; 72588</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54963; 78516</t>
+          <t>56652; 78768</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38970; 59833</t>
+          <t>39147; 59569</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25476; 44096</t>
+          <t>25765; 43005</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97628; 127921</t>
+          <t>96017; 126193</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108045; 140057</t>
+          <t>105508; 137754</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79747; 106725</t>
+          <t>79663; 106249</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50628; 74758</t>
+          <t>51473; 74910</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13877; 27030</t>
+          <t>14441; 27693</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20296; 35906</t>
+          <t>20287; 35713</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24385; 42140</t>
+          <t>25330; 42840</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22811; 43009</t>
+          <t>23117; 42724</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20566; 36641</t>
+          <t>20815; 35289</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13673; 28225</t>
+          <t>13940; 27354</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27089; 44462</t>
+          <t>26678; 43970</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27464; 48259</t>
+          <t>27393; 47498</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37700; 58453</t>
+          <t>37269; 57180</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37659; 59584</t>
+          <t>36267; 57842</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57386; 82719</t>
+          <t>56726; 81255</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55444; 85362</t>
+          <t>55135; 83433</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13847; 27781</t>
+          <t>13376; 27343</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14330; 28289</t>
+          <t>14298; 28922</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17242; 31949</t>
+          <t>16983; 32019</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16416; 34354</t>
+          <t>15806; 34495</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25527; 42554</t>
+          <t>24678; 41789</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18285; 33779</t>
+          <t>19065; 33329</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12621; 27089</t>
+          <t>12683; 26679</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31487; 56161</t>
+          <t>32363; 57038</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42752; 64221</t>
+          <t>43581; 65547</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36823; 57464</t>
+          <t>37080; 57597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32249; 53062</t>
+          <t>33212; 53548</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54767; 84217</t>
+          <t>53147; 82403</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>116961; 149439</t>
+          <t>116903; 151293</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>145520; 180809</t>
+          <t>145285; 183629</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128350; 163278</t>
+          <t>127645; 161928</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83926; 120598</t>
+          <t>82080; 116826</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>143277; 179505</t>
+          <t>143533; 179665</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>151924; 189534</t>
+          <t>151532; 188742</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>129406; 164987</t>
+          <t>129843; 164378</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>113277; 149728</t>
+          <t>113296; 151520</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>271234; 317509</t>
+          <t>272281; 320747</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>307151; 360128</t>
+          <t>307721; 361743</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>264740; 313988</t>
+          <t>266751; 316631</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>206386; 259768</t>
+          <t>207822; 258123</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP17-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33,07%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39,81%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34,56%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30,38%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>41,2%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>41,06%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>33,75%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,56%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,12; 48,08</t>
+          <t>26,57; 40,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,19; 47,92</t>
+          <t>33,16; 46,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,53; 40,27</t>
+          <t>28,31; 42,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,1; 37,93</t>
+          <t>22,2; 39,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,83; 39,76</t>
+          <t>33,99; 48,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,54; 46,65</t>
+          <t>34,36; 47,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,86; 41,39</t>
+          <t>27,38; 40,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,98; 40,08</t>
+          <t>19,78; 38,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,91; 41,59</t>
+          <t>31,61; 42,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,95; 45,56</t>
+          <t>35,9; 44,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,38; 38,73</t>
+          <t>29,7; 38,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,83; 35,51</t>
+          <t>23,55; 35,7</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,01%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>19,67%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>23,33%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>20,52%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,01%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,58; 23,91</t>
+          <t>20,07; 28,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 27,89</t>
+          <t>21,0; 30,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,11; 24,45</t>
+          <t>15,33; 23,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 23,57</t>
+          <t>13,99; 23,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,86; 28,61</t>
+          <t>16,16; 24,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,11; 29,36</t>
+          <t>18,72; 28,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,2; 23,14</t>
+          <t>16,52; 25,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 23,56</t>
+          <t>12,6; 22,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,94; 24,89</t>
+          <t>18,96; 25,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,94; 27,34</t>
+          <t>21,13; 27,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 22,7</t>
+          <t>16,77; 22,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,06; 21,91</t>
+          <t>15,04; 21,52</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,16%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,77%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>15,48%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>17,25%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>17,38%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,16%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,32; 21,71</t>
+          <t>14,06; 25,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,97; 22,84</t>
+          <t>8,53; 17,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,45; 22,75</t>
+          <t>14,59; 24,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,36; 24,69</t>
+          <t>12,98; 22,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,71; 24,94</t>
+          <t>10,83; 20,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 17,32</t>
+          <t>12,8; 22,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 23,57</t>
+          <t>13,33; 22,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,89; 22,35</t>
+          <t>12,09; 22,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 21,25</t>
+          <t>14,11; 21,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,54; 18,4</t>
+          <t>11,84; 18,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,13; 21,68</t>
+          <t>14,99; 21,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 21,64</t>
+          <t>13,97; 20,7</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10,46%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,9%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 14,09</t>
+          <t>12,44; 20,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,88</t>
+          <t>10,41; 18,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 18,55</t>
+          <t>7,22; 15,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 12,52</t>
+          <t>10,48; 18,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 20,28</t>
+          <t>7,37; 14,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 18,62</t>
+          <t>8,45; 16,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,39</t>
+          <t>9,99; 18,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 18,67</t>
+          <t>6,98; 13,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 16,38</t>
+          <t>10,76; 16,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 16,44</t>
+          <t>10,53; 16,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 15,48</t>
+          <t>9,5; 15,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 14,18</t>
+          <t>9,77; 14,9</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>19,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 22,22</t>
+          <t>19,96; 24,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,46; 25,86</t>
+          <t>20,18; 25,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,16; 23,03</t>
+          <t>17,19; 22,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,34; 17,56</t>
+          <t>15,03; 19,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,86; 24,86</t>
+          <t>17,38; 22,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,17; 25,13</t>
+          <t>20,19; 25,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,53; 22,19</t>
+          <t>18,03; 22,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,89</t>
+          <t>13,0; 17,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 22,85</t>
+          <t>19,4; 22,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,06; 24,76</t>
+          <t>21,05; 24,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 21,93</t>
+          <t>18,44; 21,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,56; 18,08</t>
+          <t>14,73; 18,15</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>40141</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58112</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42687</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>43745</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>60262</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>44437</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>40141</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58112</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42687</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35161; 51043</t>
+          <t>32253; 48888</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51639; 70321</t>
+          <t>48406; 68055</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36239; 53012</t>
+          <t>34961; 51917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11560; 21816</t>
+          <t>11220; 19969</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32564; 48263</t>
+          <t>36086; 51896</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48963; 68100</t>
+          <t>50429; 69886</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34414; 51118</t>
+          <t>36044; 53214</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13504; 24626</t>
+          <t>10304; 20216</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>72605; 94637</t>
+          <t>71935; 96046</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105250; 133365</t>
+          <t>105101; 130908</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74966; 98816</t>
+          <t>75778; 98712</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28347; 42241</t>
+          <t>24164; 36637</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61062</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67207</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48947</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>49802</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>54949</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>43195</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>61062</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67207</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>48947</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39441; 60535</t>
+          <t>50924; 72354</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44211; 65674</t>
+          <t>56346; 81213</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33909; 51467</t>
+          <t>39459; 59926</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20977; 37554</t>
+          <t>22041; 37536</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50392; 72588</t>
+          <t>40922; 61539</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56652; 78768</t>
+          <t>44075; 66782</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39147; 59569</t>
+          <t>34774; 53095</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25765; 43005</t>
+          <t>18330; 33058</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96017; 126193</t>
+          <t>96095; 127056</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105508; 137754</t>
+          <t>106477; 139633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79663; 106249</t>
+          <t>78487; 106217</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51473; 74910</t>
+          <t>45567; 65224</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27442</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19852</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35739</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>19738</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>26967</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>32733</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>27442</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19852</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>35739</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14441; 27693</t>
+          <t>19904; 35871</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20287; 35713</t>
+          <t>13468; 27177</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25330; 42840</t>
+          <t>27220; 45546</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23117; 42724</t>
+          <t>25970; 45803</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20815; 35289</t>
+          <t>13817; 26626</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13940; 27354</t>
+          <t>20017; 35331</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26678; 43970</t>
+          <t>25109; 42964</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27393; 47498</t>
+          <t>21115; 38866</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37269; 57180</t>
+          <t>37960; 57409</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36267; 57842</t>
+          <t>37220; 57412</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56726; 81255</t>
+          <t>56181; 80555</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55135; 83433</t>
+          <t>52360; 77589</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33191</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25410</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18746</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20302</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20967</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>23521</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>33191</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25410</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18746</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13376; 27343</t>
+          <t>25637; 42764</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14298; 28922</t>
+          <t>18624; 33134</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16983; 32019</t>
+          <t>12511; 26453</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15806; 34495</t>
+          <t>30658; 54410</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24678; 41789</t>
+          <t>14310; 28644</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19065; 33329</t>
+          <t>14484; 29066</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12683; 26679</t>
+          <t>17239; 31952</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32363; 57038</t>
+          <t>17912; 34566</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43581; 65547</t>
+          <t>43036; 64709</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37080; 57597</t>
+          <t>36884; 58100</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33212; 53548</t>
+          <t>32868; 52605</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53147; 82403</t>
+          <t>53667; 81807</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>133587</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>163145</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>143886</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>161836</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>170581</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>146119</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>116903; 151293</t>
+          <t>144249; 180387</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>145285; 183629</t>
+          <t>151559; 189799</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127645; 161928</t>
+          <t>127328; 163833</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82080; 116826</t>
+          <t>105312; 138293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>143533; 179665</t>
+          <t>118374; 150599</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>151532; 188742</t>
+          <t>143342; 180478</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>129843; 164378</t>
+          <t>126750; 161597</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>113296; 151520</t>
+          <t>81764; 111378</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>272281; 320747</t>
+          <t>272305; 320612</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>307721; 361743</t>
+          <t>307512; 360492</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>266751; 316631</t>
+          <t>266309; 314781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>207822; 258123</t>
+          <t>195795; 241364</t>
         </is>
       </c>
     </row>
